--- a/artfynd/A 61173-2024 artfynd.xlsx
+++ b/artfynd/A 61173-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122068</v>
       </c>
       <c r="B2" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61173-2024 artfynd.xlsx
+++ b/artfynd/A 61173-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122068</v>
       </c>
       <c r="B2" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61173-2024 artfynd.xlsx
+++ b/artfynd/A 61173-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122068</v>
       </c>
       <c r="B2" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61173-2024 artfynd.xlsx
+++ b/artfynd/A 61173-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136122068</v>
       </c>
       <c r="B2" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
